--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CEF9D1-9072-4ADD-8B71-A39068E4B433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E0C222-BC14-4273-BB21-FD94A1DCA2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{C42FA279-E8B3-4402-922D-DA72FD085F98}"/>
   </bookViews>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E0C222-BC14-4273-BB21-FD94A1DCA2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5CA423-BB99-4669-B6DD-E35BF87614E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{C42FA279-E8B3-4402-922D-DA72FD085F98}"/>
   </bookViews>
@@ -1622,11 +1622,11 @@
         <v>74</v>
       </c>
       <c r="B30" s="10">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="C30" s="8">
         <f t="shared" si="0"/>
-        <v>411.97473221642406</v>
+        <v>274.64982147761606</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>75</v>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5CA423-BB99-4669-B6DD-E35BF87614E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE76245-BF1D-4E57-A912-651F74351069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{C42FA279-E8B3-4402-922D-DA72FD085F98}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
   <si>
     <t>banana plug 2mm pair 10pcs</t>
   </si>
@@ -259,15 +259,6 @@
   </si>
   <si>
     <t>for sensors</t>
-  </si>
-  <si>
-    <t>I will rob most of the resistors and capacitors from by brother :)</t>
-  </si>
-  <si>
-    <t>My brother</t>
-  </si>
-  <si>
-    <t>He said it is okay tho :)</t>
   </si>
   <si>
     <t>like MCU, connector, buck conv, MOSFETs… Letme know if anyone need exact BOM here</t>
@@ -1619,7 +1610,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B30" s="10">
         <v>1000</v>
@@ -1629,15 +1620,15 @@
         <v>274.64982147761606</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B31" s="10">
         <v>500</v>
@@ -1647,10 +1638,10 @@
         <v>137.32491073880803</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1659,109 +1650,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C35" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C36" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C37" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C38" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C39" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="10">
-        <v>0</v>
-      </c>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C40" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C41" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C42" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C43" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C44" s="8">
         <f>#REF!/$H$2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C45" s="8">
         <f>#REF!/$H$2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C46" s="8">
         <f>#REF!/$H$2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C47" s="8">
         <f>#REF!/$H$2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C48" s="8">
         <f>#REF!/$H$2</f>
         <v>0</v>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE76245-BF1D-4E57-A912-651F74351069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{3BF1B69B-FAC5-40F8-B2F5-189FD527CE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{C42FA279-E8B3-4402-922D-DA72FD085F98}"/>
+    <workbookView xWindow="-28920" yWindow="2730" windowWidth="29040" windowHeight="15840" xr2:uid="{C42FA279-E8B3-4402-922D-DA72FD085F98}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="86">
   <si>
     <t>banana plug 2mm pair 10pcs</t>
   </si>
@@ -162,9 +163,6 @@
     <t>3psc of dc motors (one more, beacuse it will burn i am worried)</t>
   </si>
   <si>
-    <t>RS-385SH dc motor 3pcs</t>
-  </si>
-  <si>
     <t>Lasercut locally</t>
   </si>
   <si>
@@ -174,42 +172,15 @@
     <t>i found cheap offer locally</t>
   </si>
   <si>
-    <t>spring steel front (0.1mm thicl)</t>
-  </si>
-  <si>
-    <t>i emailed about 6 companies locally - only one responded…</t>
-  </si>
-  <si>
     <t>PCBs 4 layer</t>
   </si>
   <si>
-    <t>JLCPCB</t>
-  </si>
-  <si>
     <t>2 motors 1 controller</t>
   </si>
   <si>
-    <t>BJ parts from metal</t>
-  </si>
-  <si>
-    <t>JLC3DP</t>
-  </si>
-  <si>
     <t>gearboxes, mounts</t>
   </si>
   <si>
-    <t>CNC Aluminium front part</t>
-  </si>
-  <si>
-    <t>CNC front plow from hard steel 2 pieces</t>
-  </si>
-  <si>
-    <t>JLCCNC</t>
-  </si>
-  <si>
-    <t>hard to design tbh…</t>
-  </si>
-  <si>
     <t>one may go dull at the competition. A sumo robot with dull plow is a robot who already lost…</t>
   </si>
   <si>
@@ -276,7 +247,67 @@
     <t>Fast laser distance sensors 5pcs</t>
   </si>
   <si>
-    <t>crazy expensive. Cracy fast. Crazy accurate. I want to buy +1pcs beacuse im worried of issues at the competition abroad</t>
+    <t>RS-385 dc motor 3 pcs</t>
+  </si>
+  <si>
+    <t>1mm sturdy metal back - laser cut</t>
+  </si>
+  <si>
+    <t>2mm metal ceil - laser cut</t>
+  </si>
+  <si>
+    <t>MJF gearboxes - 1kg weight class</t>
+  </si>
+  <si>
+    <t>MJF wheel hubs</t>
+  </si>
+  <si>
+    <t>for wheels and axes</t>
+  </si>
+  <si>
+    <t>Nylon SLS gearboxes - 0.5kg weight class</t>
+  </si>
+  <si>
+    <t>Nylon SLS rims for wheels</t>
+  </si>
+  <si>
+    <t>Whellie wheels</t>
+  </si>
+  <si>
+    <t>Moer lightweight but less rigid</t>
+  </si>
+  <si>
+    <t>other Nylon SLS parts, PCB holder etc</t>
+  </si>
+  <si>
+    <t>motor drivers pcb holder, bearings holder</t>
+  </si>
+  <si>
+    <t>MJF steel front part</t>
+  </si>
+  <si>
+    <t>as sturdy as one could get</t>
+  </si>
+  <si>
+    <t>CNC front plow/wedge, steel alloy, blackening. I recommend 2 pcc</t>
+  </si>
+  <si>
+    <t>JLC -10 bucks cupon</t>
+  </si>
+  <si>
+    <t>I wanted to include it lol</t>
+  </si>
+  <si>
+    <t>Not-so-cheap, but cracy fast and crazy accurate. I recommend +1 pcs beacuse you can burn them easly</t>
+  </si>
+  <si>
+    <t>My friends time, spent painting ceil to be pretty</t>
+  </si>
+  <si>
+    <t>priceless</t>
+  </si>
+  <si>
+    <t>friends which leave nearby c.o.o.</t>
   </si>
 </sst>
 </file>
@@ -286,7 +317,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,6 +356,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -334,7 +374,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -434,8 +474,47 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -445,99 +524,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -546,46 +537,47 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="6">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
         <top/>
         <bottom/>
         <vertical/>
@@ -610,7 +602,9 @@
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
         <right style="medium">
           <color indexed="64"/>
         </right>
@@ -626,16 +620,6 @@
         <left style="medium">
           <color indexed="64"/>
         </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
         <right style="medium">
           <color indexed="64"/>
         </right>
@@ -646,16 +630,17 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -728,16 +713,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{892F83E0-4F5A-4DCE-B799-55AFFBAC1306}" name="Table1" displayName="Table1" ref="A1:E1048576" totalsRowShown="0" headerRowBorderDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="A1:E1048576" xr:uid="{892F83E0-4F5A-4DCE-B799-55AFFBAC1306}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ADEFC003-3ECE-490E-8BFB-00AE78A6C921}" name="Table1" displayName="Table1" ref="A1:E1048576" totalsRowShown="0" headerRowBorderDxfId="5">
+  <autoFilter ref="A1:E1048576" xr:uid="{ADEFC003-3ECE-490E-8BFB-00AE78A6C921}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4C012F1F-09CC-4782-AB83-3B08A3F28665}" name="What" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{C1C314BE-AF80-4F97-ADC6-98A693A7E132}" name="Cost in PLN" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{C19B8432-EEA8-4DD7-AA5D-B07CD66BD721}" name="Cost in USD" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{290D7BE8-0EE4-4B80-8641-0F9E56F7EC8A}" name="Where to buy" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{DEB17377-0C21-4C91-A585-B5822B267936}" name="Comment (if needed)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C846A738-6CD5-4EEA-A213-6ABC5EEC35D3}" name="What" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{099FC836-4D16-4DCA-9FBD-D0D34ACB6948}" name="Cost in PLN" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{77D6C98E-6D39-4446-BD42-BC46D35DB797}" name="Cost in USD" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{1E0DC335-9E61-4E69-A61F-8DE1AE92EA62}" name="Where to buy" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{9414348B-7AFA-4FBE-912C-B3D89114E8C4}" name="Comment (if needed)" dataDxfId="4"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1058,32 +1043,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6354B0EA-FD67-41B9-8CE3-61AA3DD76543}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59" style="16" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="31.85546875" style="12" customWidth="1"/>
-    <col min="5" max="5" width="106.85546875" style="17" customWidth="1"/>
+    <col min="1" max="1" width="62.42578125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="31.85546875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="111" style="10" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="9" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -1091,20 +1076,20 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="13">
         <v>5.05</v>
       </c>
-      <c r="C2" s="8">
-        <f>B2/$H$2</f>
+      <c r="C2" s="7">
+        <f t="shared" ref="C2:C21" si="0">B2/$H$2</f>
         <v>1.3869815984619609</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="17" t="s">
+      <c r="D2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>33</v>
       </c>
       <c r="H2" s="6">
@@ -1112,789 +1097,668 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="14">
         <v>5.79</v>
       </c>
-      <c r="C3" s="8">
-        <f t="shared" ref="C3:C43" si="0">B3/$H$2</f>
+      <c r="C3" s="7">
+        <f t="shared" si="0"/>
         <v>1.5902224663553968</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="15">
         <v>6.91</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <f t="shared" si="0"/>
         <v>1.8978302664103268</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="17" t="s">
+      <c r="D4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="5">
-        <f>SUM(#REF!)/H2</f>
-        <v>791.15078275199119</v>
+        <f>SUM(C:C)</f>
+        <v>792.44533095303495</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="15">
         <v>7.89</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <f t="shared" si="0"/>
         <v>2.1669870914583904</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="4">
-        <f>SUM(#REF!)</f>
-        <v>2880.58</v>
+        <f>SUM(B:B)</f>
+        <v>2921.70345</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="15">
         <v>19.77</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <f t="shared" si="0"/>
         <v>5.4298269706124689</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="14">
         <v>3.35</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <f t="shared" si="0"/>
         <v>0.92007690195001379</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="14">
         <v>14.49</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <f t="shared" si="0"/>
         <v>3.9796759132106563</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="14">
         <v>18.510000000000002</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <f t="shared" si="0"/>
         <v>5.0837681955506735</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>44.82</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <f t="shared" si="0"/>
         <v>12.309804998626751</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="14">
         <v>14.78</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <f t="shared" si="0"/>
         <v>4.059324361439165</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="17" t="s">
+      <c r="D11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="14">
         <v>5.68</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <f t="shared" si="0"/>
         <v>1.560010985992859</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="D12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="14">
         <v>5</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <f t="shared" si="0"/>
         <v>1.3732491073880801</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="17" t="s">
+      <c r="D13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="14">
         <v>5.44</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <f t="shared" si="0"/>
         <v>1.4940950288382313</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="D14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="14">
         <v>7.14</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <f t="shared" si="0"/>
         <v>1.9609997253501785</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="17" t="s">
+      <c r="D15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="14">
+        <v>45.96</v>
+      </c>
+      <c r="C16" s="7">
+        <f t="shared" si="0"/>
+        <v>12.622905795111233</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="14">
+        <v>30</v>
+      </c>
+      <c r="C17" s="7">
+        <f t="shared" si="0"/>
+        <v>8.2394946443284809</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="7">
-        <v>45.96</v>
-      </c>
-      <c r="C16" s="8">
-        <f t="shared" si="0"/>
-        <v>12.622905795111233</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="7">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="14">
+        <v>30</v>
+      </c>
+      <c r="C18" s="7">
+        <f t="shared" si="0"/>
+        <v>8.2394946443284809</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="7">
+        <v>30</v>
+      </c>
+      <c r="C19" s="7">
+        <f t="shared" si="0"/>
+        <v>8.2394946443284809</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="7">
+        <v>100</v>
+      </c>
+      <c r="C20" s="7">
+        <f t="shared" si="0"/>
+        <v>27.464982147761603</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="7">
+        <v>220</v>
+      </c>
+      <c r="C21" s="7">
+        <f t="shared" si="0"/>
+        <v>60.422960725075527</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="7">
+        <f>#REF!*$H$2</f>
+        <v>54.615000000000002</v>
+      </c>
+      <c r="C22" s="7">
+        <v>15</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="7">
+        <f>#REF!*$H$2</f>
+        <v>29.128</v>
+      </c>
+      <c r="C23" s="7">
+        <v>8</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="7">
+        <f>#REF!*$H$2</f>
+        <v>14.564</v>
+      </c>
+      <c r="C24" s="7">
+        <v>4</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="7">
+        <f>#REF!*$H$2</f>
+        <v>14.564</v>
+      </c>
+      <c r="C25" s="7">
+        <v>4</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="7">
+        <f>#REF!*$H$2</f>
+        <v>143.63745</v>
+      </c>
+      <c r="C26" s="7">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="7">
+        <v>280</v>
+      </c>
+      <c r="C27" s="7">
+        <f>B27/$H$2</f>
+        <v>76.901950013732488</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="7">
+        <f>#REF!*H2</f>
+        <v>54.615000000000002</v>
+      </c>
+      <c r="C28" s="7">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="7">
+        <f>#REF!*H3</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-10</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="7">
+        <v>50</v>
+      </c>
+      <c r="C30" s="7">
+        <f t="shared" ref="C30:C37" si="1">B30/$H$2</f>
+        <v>13.732491073880801</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45</v>
+      </c>
+      <c r="C31" s="7">
+        <f t="shared" si="1"/>
+        <v>12.359241966492721</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="7">
+        <v>50</v>
+      </c>
+      <c r="C32" s="7">
+        <f t="shared" si="1"/>
+        <v>13.732491073880801</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="7">
+        <v>20</v>
+      </c>
+      <c r="C33" s="7">
+        <f t="shared" si="1"/>
+        <v>5.4929964295523206</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="7">
+        <v>25</v>
+      </c>
+      <c r="C34" s="7">
+        <f t="shared" si="1"/>
+        <v>6.8662455369404007</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="7">
+        <v>20</v>
+      </c>
+      <c r="C35" s="7">
+        <f t="shared" si="1"/>
+        <v>5.4929964295523206</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="7">
+        <v>1000</v>
+      </c>
+      <c r="C36" s="7">
+        <f t="shared" si="1"/>
+        <v>274.64982147761606</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="8">
-        <f t="shared" si="0"/>
-        <v>16.478989288656962</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="7">
-        <v>150</v>
-      </c>
-      <c r="C18" s="8">
-        <f t="shared" si="0"/>
-        <v>41.197473221642404</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="10">
-        <v>50</v>
-      </c>
-      <c r="C19" s="8">
-        <f t="shared" si="0"/>
-        <v>13.732491073880801</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="7">
-        <v>250</v>
-      </c>
-      <c r="C20" s="8">
-        <f t="shared" si="0"/>
-        <v>68.662455369404015</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="7">
-        <v>250</v>
-      </c>
-      <c r="C21" s="8">
-        <f t="shared" si="0"/>
-        <v>68.662455369404015</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="7">
-        <v>200</v>
-      </c>
-      <c r="C22" s="8">
-        <f t="shared" si="0"/>
-        <v>54.929964295523206</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="8">
-        <f t="shared" si="0"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="7">
+        <v>500</v>
+      </c>
+      <c r="C37" s="7">
+        <f t="shared" si="1"/>
+        <v>137.32491073880803</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="7">
         <v>0</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="10">
-        <v>50</v>
-      </c>
-      <c r="C24" s="8">
-        <f t="shared" si="0"/>
-        <v>13.732491073880801</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="10">
-        <v>45</v>
-      </c>
-      <c r="C25" s="8">
-        <f t="shared" si="0"/>
-        <v>12.359241966492721</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="10">
-        <v>50</v>
-      </c>
-      <c r="C26" s="8">
-        <f t="shared" si="0"/>
-        <v>13.732491073880801</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="10">
-        <v>20</v>
-      </c>
-      <c r="C27" s="8">
-        <f t="shared" si="0"/>
-        <v>5.4929964295523206</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="10">
-        <v>25</v>
-      </c>
-      <c r="C28" s="8">
-        <f t="shared" si="0"/>
-        <v>6.8662455369404007</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="10">
-        <v>20</v>
-      </c>
-      <c r="C29" s="8">
-        <f t="shared" si="0"/>
-        <v>5.4929964295523206</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" s="10">
-        <v>1000</v>
-      </c>
-      <c r="C30" s="8">
-        <f t="shared" si="0"/>
-        <v>274.64982147761606</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" s="10">
-        <v>500</v>
-      </c>
-      <c r="C31" s="8">
-        <f t="shared" si="0"/>
-        <v>137.32491073880803</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C32" s="8">
-        <f t="shared" si="0"/>
+      <c r="C38" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C36" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C37" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C38" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C39" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C40" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C41" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C42" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C43" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C44" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C45" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C46" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C47" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C48" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C49" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C50" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C51" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C52" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C53" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C54" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C55" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C56" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C57" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C58" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C59" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C60" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C61" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C62" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C63" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C64" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C65" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C66" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C67" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C68" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C69" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C70" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C71" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C72" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C73" s="8">
-        <f>#REF!/$H$2</f>
-        <v>0</v>
-      </c>
+      <c r="D38" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E39" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
